--- a/Assets/@Resources/Data/Excel/MinMonData.xlsx
+++ b/Assets/@Resources/Data/Excel/MinMonData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>젤리 퐁</t>
+          <t>Minmon2001NameText</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -660,14 +660,20 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
       </c>
       <c r="M4" t="n">
         <v>10</v>
@@ -682,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라비 슬라임</t>
+          <t>Minmon2002NameText</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -704,20 +710,84 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
       </c>
       <c r="M5" t="n">
         <v>12</v>
       </c>
       <c r="N5" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GoblinNameText</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>goblin_monster_0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Goblin</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/MinMonData.xlsx
+++ b/Assets/@Resources/Data/Excel/MinMonData.xlsx
@@ -536,17 +536,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -563,32 +563,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미니몬 고유 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>이름(로컬키)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>아이콘 라벨</t>
+          <t>아이콘</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>프리팹 라벨</t>
+          <t>프리팹</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>펫 애니 라벨</t>
+          <t>펫 애니</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>원본 몬스터 ID</t>
+          <t>원본 몬스터ID</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>기본 공격속도</t>
+          <t>기본 공속</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>기본 치명타율</t>
+          <t>기본 치명%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>최대 길들이기 횟수</t>
+          <t>최대 길들이기</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -691,7 +691,11 @@
           <t>Minmon2002NameText</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Slime_Antenna_Idle_4</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>

--- a/Assets/@Resources/Data/Excel/MinMonData.xlsx
+++ b/Assets/@Resources/Data/Excel/MinMonData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N506"/>
+  <dimension ref="A1:P506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,16 @@
           <t>CatchChance</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>FirstInterestKillCount</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>FirstCatchChance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +569,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -629,6 +649,16 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>포획 확률(0~1)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>미보유 첫 관심 보장 처치수(0=미사용)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>첫 포획 확률(0=기존 확률)</t>
         </is>
       </c>
     </row>
@@ -679,6 +709,12 @@
       <c r="N4" t="n">
         <v>0.1</v>
       </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -732,6 +768,12 @@
       <c r="N5" t="n">
         <v>0.08</v>
       </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -790,6 +832,12 @@
       <c r="N6" t="n">
         <v>0.1</v>
       </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -848,6 +896,12 @@
       <c r="N7" t="n">
         <v>0.3</v>
       </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -906,6 +960,12 @@
       <c r="N8" t="n">
         <v>0.3</v>
       </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -964,6 +1024,12 @@
       <c r="N9" t="n">
         <v>0.3</v>
       </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1022,6 +1088,12 @@
       <c r="N10" t="n">
         <v>0.3</v>
       </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1080,6 +1152,12 @@
       <c r="N11" t="n">
         <v>0.21</v>
       </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1138,6 +1216,12 @@
       <c r="N12" t="n">
         <v>0.3</v>
       </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1196,6 +1280,12 @@
       <c r="N13" t="n">
         <v>0.3</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1254,6 +1344,12 @@
       <c r="N14" t="n">
         <v>0.3</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1312,6 +1408,12 @@
       <c r="N15" t="n">
         <v>0.3</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1370,6 +1472,12 @@
       <c r="N16" t="n">
         <v>0.21</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1428,6 +1536,12 @@
       <c r="N17" t="n">
         <v>0.3</v>
       </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1486,6 +1600,12 @@
       <c r="N18" t="n">
         <v>0.3</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1544,6 +1664,12 @@
       <c r="N19" t="n">
         <v>0.3</v>
       </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1602,6 +1728,12 @@
       <c r="N20" t="n">
         <v>0.3</v>
       </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1660,6 +1792,12 @@
       <c r="N21" t="n">
         <v>0.21</v>
       </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1718,6 +1856,12 @@
       <c r="N22" t="n">
         <v>0.3</v>
       </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1776,6 +1920,12 @@
       <c r="N23" t="n">
         <v>0.12</v>
       </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1834,6 +1984,12 @@
       <c r="N24" t="n">
         <v>0.28</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1892,6 +2048,12 @@
       <c r="N25" t="n">
         <v>0.28</v>
       </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1950,6 +2112,12 @@
       <c r="N26" t="n">
         <v>0.28</v>
       </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2008,6 +2176,12 @@
       <c r="N27" t="n">
         <v>0.28</v>
       </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2066,6 +2240,12 @@
       <c r="N28" t="n">
         <v>0.196</v>
       </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2124,6 +2304,12 @@
       <c r="N29" t="n">
         <v>0.28</v>
       </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2182,6 +2368,12 @@
       <c r="N30" t="n">
         <v>0.28</v>
       </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2240,6 +2432,12 @@
       <c r="N31" t="n">
         <v>0.28</v>
       </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2298,6 +2496,12 @@
       <c r="N32" t="n">
         <v>0.28</v>
       </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2356,6 +2560,12 @@
       <c r="N33" t="n">
         <v>0.196</v>
       </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2414,6 +2624,12 @@
       <c r="N34" t="n">
         <v>0.28</v>
       </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2472,6 +2688,12 @@
       <c r="N35" t="n">
         <v>0.28</v>
       </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2530,6 +2752,12 @@
       <c r="N36" t="n">
         <v>0.28</v>
       </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2588,6 +2816,12 @@
       <c r="N37" t="n">
         <v>0.28</v>
       </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2646,6 +2880,12 @@
       <c r="N38" t="n">
         <v>0.196</v>
       </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2704,6 +2944,12 @@
       <c r="N39" t="n">
         <v>0.28</v>
       </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2762,6 +3008,12 @@
       <c r="N40" t="n">
         <v>0.112</v>
       </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2820,6 +3072,12 @@
       <c r="N41" t="n">
         <v>0.26</v>
       </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2878,6 +3136,12 @@
       <c r="N42" t="n">
         <v>0.26</v>
       </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2936,6 +3200,12 @@
       <c r="N43" t="n">
         <v>0.26</v>
       </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2994,6 +3264,12 @@
       <c r="N44" t="n">
         <v>0.26</v>
       </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3052,6 +3328,12 @@
       <c r="N45" t="n">
         <v>0.182</v>
       </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3110,6 +3392,12 @@
       <c r="N46" t="n">
         <v>0.26</v>
       </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3168,6 +3456,12 @@
       <c r="N47" t="n">
         <v>0.26</v>
       </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3226,6 +3520,12 @@
       <c r="N48" t="n">
         <v>0.26</v>
       </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3284,6 +3584,12 @@
       <c r="N49" t="n">
         <v>0.26</v>
       </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3342,6 +3648,12 @@
       <c r="N50" t="n">
         <v>0.182</v>
       </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3400,6 +3712,12 @@
       <c r="N51" t="n">
         <v>0.26</v>
       </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3458,6 +3776,12 @@
       <c r="N52" t="n">
         <v>0.26</v>
       </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3516,6 +3840,12 @@
       <c r="N53" t="n">
         <v>0.26</v>
       </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3574,6 +3904,12 @@
       <c r="N54" t="n">
         <v>0.26</v>
       </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3632,6 +3968,12 @@
       <c r="N55" t="n">
         <v>0.182</v>
       </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3690,6 +4032,12 @@
       <c r="N56" t="n">
         <v>0.26</v>
       </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3748,6 +4096,12 @@
       <c r="N57" t="n">
         <v>0.104</v>
       </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3806,6 +4160,12 @@
       <c r="N58" t="n">
         <v>0.24</v>
       </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3864,6 +4224,12 @@
       <c r="N59" t="n">
         <v>0.24</v>
       </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3922,6 +4288,12 @@
       <c r="N60" t="n">
         <v>0.24</v>
       </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3980,6 +4352,12 @@
       <c r="N61" t="n">
         <v>0.24</v>
       </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4038,6 +4416,12 @@
       <c r="N62" t="n">
         <v>0.168</v>
       </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4096,6 +4480,12 @@
       <c r="N63" t="n">
         <v>0.24</v>
       </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4154,6 +4544,12 @@
       <c r="N64" t="n">
         <v>0.24</v>
       </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4212,6 +4608,12 @@
       <c r="N65" t="n">
         <v>0.24</v>
       </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4270,6 +4672,12 @@
       <c r="N66" t="n">
         <v>0.24</v>
       </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4328,6 +4736,12 @@
       <c r="N67" t="n">
         <v>0.168</v>
       </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4386,6 +4800,12 @@
       <c r="N68" t="n">
         <v>0.24</v>
       </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4444,6 +4864,12 @@
       <c r="N69" t="n">
         <v>0.24</v>
       </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4502,6 +4928,12 @@
       <c r="N70" t="n">
         <v>0.24</v>
       </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4560,6 +4992,12 @@
       <c r="N71" t="n">
         <v>0.24</v>
       </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4618,6 +5056,12 @@
       <c r="N72" t="n">
         <v>0.168</v>
       </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4676,6 +5120,12 @@
       <c r="N73" t="n">
         <v>0.24</v>
       </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4734,6 +5184,12 @@
       <c r="N74" t="n">
         <v>0.096</v>
       </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4792,6 +5248,12 @@
       <c r="N75" t="n">
         <v>0.22</v>
       </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4850,6 +5312,12 @@
       <c r="N76" t="n">
         <v>0.22</v>
       </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4908,6 +5376,12 @@
       <c r="N77" t="n">
         <v>0.22</v>
       </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4966,6 +5440,12 @@
       <c r="N78" t="n">
         <v>0.22</v>
       </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5024,6 +5504,12 @@
       <c r="N79" t="n">
         <v>0.154</v>
       </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5082,6 +5568,12 @@
       <c r="N80" t="n">
         <v>0.22</v>
       </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5140,6 +5632,12 @@
       <c r="N81" t="n">
         <v>0.22</v>
       </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5198,6 +5696,12 @@
       <c r="N82" t="n">
         <v>0.22</v>
       </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5256,6 +5760,12 @@
       <c r="N83" t="n">
         <v>0.22</v>
       </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5314,6 +5824,12 @@
       <c r="N84" t="n">
         <v>0.154</v>
       </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5372,6 +5888,12 @@
       <c r="N85" t="n">
         <v>0.22</v>
       </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5430,6 +5952,12 @@
       <c r="N86" t="n">
         <v>0.22</v>
       </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5488,6 +6016,12 @@
       <c r="N87" t="n">
         <v>0.22</v>
       </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5546,6 +6080,12 @@
       <c r="N88" t="n">
         <v>0.22</v>
       </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5604,6 +6144,12 @@
       <c r="N89" t="n">
         <v>0.154</v>
       </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5662,6 +6208,12 @@
       <c r="N90" t="n">
         <v>0.22</v>
       </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5720,6 +6272,12 @@
       <c r="N91" t="n">
         <v>0.08799999999999999</v>
       </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5778,6 +6336,12 @@
       <c r="N92" t="n">
         <v>0.2</v>
       </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5836,6 +6400,12 @@
       <c r="N93" t="n">
         <v>0.2</v>
       </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5894,6 +6464,12 @@
       <c r="N94" t="n">
         <v>0.2</v>
       </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5952,6 +6528,12 @@
       <c r="N95" t="n">
         <v>0.2</v>
       </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6010,6 +6592,12 @@
       <c r="N96" t="n">
         <v>0.14</v>
       </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6068,6 +6656,12 @@
       <c r="N97" t="n">
         <v>0.2</v>
       </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6126,6 +6720,12 @@
       <c r="N98" t="n">
         <v>0.2</v>
       </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6184,6 +6784,12 @@
       <c r="N99" t="n">
         <v>0.2</v>
       </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6242,6 +6848,12 @@
       <c r="N100" t="n">
         <v>0.2</v>
       </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6300,6 +6912,12 @@
       <c r="N101" t="n">
         <v>0.14</v>
       </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6358,6 +6976,12 @@
       <c r="N102" t="n">
         <v>0.2</v>
       </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6416,6 +7040,12 @@
       <c r="N103" t="n">
         <v>0.2</v>
       </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6474,6 +7104,12 @@
       <c r="N104" t="n">
         <v>0.2</v>
       </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6532,6 +7168,12 @@
       <c r="N105" t="n">
         <v>0.2</v>
       </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6590,6 +7232,12 @@
       <c r="N106" t="n">
         <v>0.14</v>
       </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6648,6 +7296,12 @@
       <c r="N107" t="n">
         <v>0.2</v>
       </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6706,6 +7360,12 @@
       <c r="N108" t="n">
         <v>0.08</v>
       </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6764,6 +7424,12 @@
       <c r="N109" t="n">
         <v>0.18</v>
       </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6822,6 +7488,12 @@
       <c r="N110" t="n">
         <v>0.18</v>
       </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6880,6 +7552,12 @@
       <c r="N111" t="n">
         <v>0.18</v>
       </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6938,6 +7616,12 @@
       <c r="N112" t="n">
         <v>0.18</v>
       </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6996,6 +7680,12 @@
       <c r="N113" t="n">
         <v>0.126</v>
       </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7054,6 +7744,12 @@
       <c r="N114" t="n">
         <v>0.18</v>
       </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7112,6 +7808,12 @@
       <c r="N115" t="n">
         <v>0.18</v>
       </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7170,6 +7872,12 @@
       <c r="N116" t="n">
         <v>0.18</v>
       </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7228,6 +7936,12 @@
       <c r="N117" t="n">
         <v>0.18</v>
       </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7286,6 +8000,12 @@
       <c r="N118" t="n">
         <v>0.126</v>
       </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7344,6 +8064,12 @@
       <c r="N119" t="n">
         <v>0.18</v>
       </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7402,6 +8128,12 @@
       <c r="N120" t="n">
         <v>0.18</v>
       </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7460,6 +8192,12 @@
       <c r="N121" t="n">
         <v>0.18</v>
       </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7518,6 +8256,12 @@
       <c r="N122" t="n">
         <v>0.18</v>
       </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7576,6 +8320,12 @@
       <c r="N123" t="n">
         <v>0.126</v>
       </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7634,6 +8384,12 @@
       <c r="N124" t="n">
         <v>0.18</v>
       </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7692,6 +8448,12 @@
       <c r="N125" t="n">
         <v>0.07199999999999999</v>
       </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7750,6 +8512,12 @@
       <c r="N126" t="n">
         <v>0.16</v>
       </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7808,6 +8576,12 @@
       <c r="N127" t="n">
         <v>0.16</v>
       </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7866,6 +8640,12 @@
       <c r="N128" t="n">
         <v>0.16</v>
       </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7924,6 +8704,12 @@
       <c r="N129" t="n">
         <v>0.16</v>
       </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7982,6 +8768,12 @@
       <c r="N130" t="n">
         <v>0.112</v>
       </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8040,6 +8832,12 @@
       <c r="N131" t="n">
         <v>0.16</v>
       </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8098,6 +8896,12 @@
       <c r="N132" t="n">
         <v>0.16</v>
       </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8156,6 +8960,12 @@
       <c r="N133" t="n">
         <v>0.16</v>
       </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8214,6 +9024,12 @@
       <c r="N134" t="n">
         <v>0.16</v>
       </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8272,6 +9088,12 @@
       <c r="N135" t="n">
         <v>0.112</v>
       </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8330,6 +9152,12 @@
       <c r="N136" t="n">
         <v>0.16</v>
       </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8388,6 +9216,12 @@
       <c r="N137" t="n">
         <v>0.16</v>
       </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8446,6 +9280,12 @@
       <c r="N138" t="n">
         <v>0.16</v>
       </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8504,6 +9344,12 @@
       <c r="N139" t="n">
         <v>0.16</v>
       </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8562,6 +9408,12 @@
       <c r="N140" t="n">
         <v>0.112</v>
       </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8620,6 +9472,12 @@
       <c r="N141" t="n">
         <v>0.16</v>
       </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8678,6 +9536,12 @@
       <c r="N142" t="n">
         <v>0.064</v>
       </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8736,6 +9600,12 @@
       <c r="N143" t="n">
         <v>0.14</v>
       </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8794,6 +9664,12 @@
       <c r="N144" t="n">
         <v>0.14</v>
       </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8852,6 +9728,12 @@
       <c r="N145" t="n">
         <v>0.14</v>
       </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8910,6 +9792,12 @@
       <c r="N146" t="n">
         <v>0.14</v>
       </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8968,6 +9856,12 @@
       <c r="N147" t="n">
         <v>0.098</v>
       </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -9026,6 +9920,12 @@
       <c r="N148" t="n">
         <v>0.14</v>
       </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -9084,6 +9984,12 @@
       <c r="N149" t="n">
         <v>0.14</v>
       </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -9142,6 +10048,12 @@
       <c r="N150" t="n">
         <v>0.14</v>
       </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9200,6 +10112,12 @@
       <c r="N151" t="n">
         <v>0.14</v>
       </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9258,6 +10176,12 @@
       <c r="N152" t="n">
         <v>0.098</v>
       </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9316,6 +10240,12 @@
       <c r="N153" t="n">
         <v>0.14</v>
       </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9374,6 +10304,12 @@
       <c r="N154" t="n">
         <v>0.14</v>
       </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9432,6 +10368,12 @@
       <c r="N155" t="n">
         <v>0.14</v>
       </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9490,6 +10432,12 @@
       <c r="N156" t="n">
         <v>0.14</v>
       </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9548,6 +10496,12 @@
       <c r="N157" t="n">
         <v>0.098</v>
       </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9606,6 +10560,12 @@
       <c r="N158" t="n">
         <v>0.14</v>
       </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9664,6 +10624,12 @@
       <c r="N159" t="n">
         <v>0.056</v>
       </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9722,6 +10688,12 @@
       <c r="N160" t="n">
         <v>0.12</v>
       </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9780,6 +10752,12 @@
       <c r="N161" t="n">
         <v>0.12</v>
       </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9838,6 +10816,12 @@
       <c r="N162" t="n">
         <v>0.12</v>
       </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9896,6 +10880,12 @@
       <c r="N163" t="n">
         <v>0.12</v>
       </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9954,6 +10944,12 @@
       <c r="N164" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -10012,6 +11008,12 @@
       <c r="N165" t="n">
         <v>0.12</v>
       </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10070,6 +11072,12 @@
       <c r="N166" t="n">
         <v>0.12</v>
       </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10128,6 +11136,12 @@
       <c r="N167" t="n">
         <v>0.12</v>
       </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10186,6 +11200,12 @@
       <c r="N168" t="n">
         <v>0.12</v>
       </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10244,6 +11264,12 @@
       <c r="N169" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10302,6 +11328,12 @@
       <c r="N170" t="n">
         <v>0.12</v>
       </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10360,6 +11392,12 @@
       <c r="N171" t="n">
         <v>0.12</v>
       </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10418,6 +11456,12 @@
       <c r="N172" t="n">
         <v>0.12</v>
       </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10476,6 +11520,12 @@
       <c r="N173" t="n">
         <v>0.12</v>
       </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10534,6 +11584,12 @@
       <c r="N174" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10592,6 +11648,12 @@
       <c r="N175" t="n">
         <v>0.12</v>
       </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10650,6 +11712,12 @@
       <c r="N176" t="n">
         <v>0.048</v>
       </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10708,6 +11776,12 @@
       <c r="N177" t="n">
         <v>0.3</v>
       </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10766,6 +11840,12 @@
       <c r="N178" t="n">
         <v>0.3</v>
       </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10824,6 +11904,12 @@
       <c r="N179" t="n">
         <v>0.3</v>
       </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10882,6 +11968,12 @@
       <c r="N180" t="n">
         <v>0.3</v>
       </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10940,6 +12032,12 @@
       <c r="N181" t="n">
         <v>0.21</v>
       </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10998,6 +12096,12 @@
       <c r="N182" t="n">
         <v>0.3</v>
       </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -11056,6 +12160,12 @@
       <c r="N183" t="n">
         <v>0.3</v>
       </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -11114,6 +12224,12 @@
       <c r="N184" t="n">
         <v>0.3</v>
       </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -11172,6 +12288,12 @@
       <c r="N185" t="n">
         <v>0.3</v>
       </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -11230,6 +12352,12 @@
       <c r="N186" t="n">
         <v>0.21</v>
       </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11288,6 +12416,12 @@
       <c r="N187" t="n">
         <v>0.3</v>
       </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11346,6 +12480,12 @@
       <c r="N188" t="n">
         <v>0.3</v>
       </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11404,6 +12544,12 @@
       <c r="N189" t="n">
         <v>0.3</v>
       </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11462,6 +12608,12 @@
       <c r="N190" t="n">
         <v>0.3</v>
       </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11520,6 +12672,12 @@
       <c r="N191" t="n">
         <v>0.21</v>
       </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11578,6 +12736,12 @@
       <c r="N192" t="n">
         <v>0.3</v>
       </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11636,6 +12800,12 @@
       <c r="N193" t="n">
         <v>0.12</v>
       </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11694,6 +12864,12 @@
       <c r="N194" t="n">
         <v>0.28</v>
       </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11752,6 +12928,12 @@
       <c r="N195" t="n">
         <v>0.28</v>
       </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11810,6 +12992,12 @@
       <c r="N196" t="n">
         <v>0.28</v>
       </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11868,6 +13056,12 @@
       <c r="N197" t="n">
         <v>0.28</v>
       </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11926,6 +13120,12 @@
       <c r="N198" t="n">
         <v>0.196</v>
       </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11984,6 +13184,12 @@
       <c r="N199" t="n">
         <v>0.28</v>
       </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -12042,6 +13248,12 @@
       <c r="N200" t="n">
         <v>0.28</v>
       </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12100,6 +13312,12 @@
       <c r="N201" t="n">
         <v>0.28</v>
       </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12158,6 +13376,12 @@
       <c r="N202" t="n">
         <v>0.28</v>
       </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12216,6 +13440,12 @@
       <c r="N203" t="n">
         <v>0.196</v>
       </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12274,6 +13504,12 @@
       <c r="N204" t="n">
         <v>0.28</v>
       </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12332,6 +13568,12 @@
       <c r="N205" t="n">
         <v>0.28</v>
       </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12390,6 +13632,12 @@
       <c r="N206" t="n">
         <v>0.28</v>
       </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12448,6 +13696,12 @@
       <c r="N207" t="n">
         <v>0.28</v>
       </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12506,6 +13760,12 @@
       <c r="N208" t="n">
         <v>0.196</v>
       </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12564,6 +13824,12 @@
       <c r="N209" t="n">
         <v>0.28</v>
       </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12622,6 +13888,12 @@
       <c r="N210" t="n">
         <v>0.112</v>
       </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12680,6 +13952,12 @@
       <c r="N211" t="n">
         <v>0.26</v>
       </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12738,6 +14016,12 @@
       <c r="N212" t="n">
         <v>0.26</v>
       </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12796,6 +14080,12 @@
       <c r="N213" t="n">
         <v>0.26</v>
       </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12854,6 +14144,12 @@
       <c r="N214" t="n">
         <v>0.26</v>
       </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12912,6 +14208,12 @@
       <c r="N215" t="n">
         <v>0.182</v>
       </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12970,6 +14272,12 @@
       <c r="N216" t="n">
         <v>0.26</v>
       </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -13028,6 +14336,12 @@
       <c r="N217" t="n">
         <v>0.26</v>
       </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -13086,6 +14400,12 @@
       <c r="N218" t="n">
         <v>0.26</v>
       </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13144,6 +14464,12 @@
       <c r="N219" t="n">
         <v>0.26</v>
       </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13202,6 +14528,12 @@
       <c r="N220" t="n">
         <v>0.182</v>
       </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13260,6 +14592,12 @@
       <c r="N221" t="n">
         <v>0.26</v>
       </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13318,6 +14656,12 @@
       <c r="N222" t="n">
         <v>0.26</v>
       </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13376,6 +14720,12 @@
       <c r="N223" t="n">
         <v>0.26</v>
       </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13434,6 +14784,12 @@
       <c r="N224" t="n">
         <v>0.26</v>
       </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13492,6 +14848,12 @@
       <c r="N225" t="n">
         <v>0.182</v>
       </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13550,6 +14912,12 @@
       <c r="N226" t="n">
         <v>0.26</v>
       </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13608,6 +14976,12 @@
       <c r="N227" t="n">
         <v>0.104</v>
       </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13666,6 +15040,12 @@
       <c r="N228" t="n">
         <v>0.24</v>
       </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -13724,6 +15104,12 @@
       <c r="N229" t="n">
         <v>0.24</v>
       </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -13782,6 +15168,12 @@
       <c r="N230" t="n">
         <v>0.24</v>
       </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -13840,6 +15232,12 @@
       <c r="N231" t="n">
         <v>0.24</v>
       </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -13898,6 +15296,12 @@
       <c r="N232" t="n">
         <v>0.168</v>
       </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -13956,6 +15360,12 @@
       <c r="N233" t="n">
         <v>0.24</v>
       </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -14014,6 +15424,12 @@
       <c r="N234" t="n">
         <v>0.24</v>
       </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -14072,6 +15488,12 @@
       <c r="N235" t="n">
         <v>0.24</v>
       </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -14130,6 +15552,12 @@
       <c r="N236" t="n">
         <v>0.24</v>
       </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -14188,6 +15616,12 @@
       <c r="N237" t="n">
         <v>0.168</v>
       </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -14246,6 +15680,12 @@
       <c r="N238" t="n">
         <v>0.24</v>
       </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -14304,6 +15744,12 @@
       <c r="N239" t="n">
         <v>0.24</v>
       </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -14362,6 +15808,12 @@
       <c r="N240" t="n">
         <v>0.24</v>
       </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -14420,6 +15872,12 @@
       <c r="N241" t="n">
         <v>0.24</v>
       </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -14478,6 +15936,12 @@
       <c r="N242" t="n">
         <v>0.168</v>
       </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -14536,6 +16000,12 @@
       <c r="N243" t="n">
         <v>0.24</v>
       </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -14594,6 +16064,12 @@
       <c r="N244" t="n">
         <v>0.096</v>
       </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -14652,6 +16128,12 @@
       <c r="N245" t="n">
         <v>0.22</v>
       </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -14710,6 +16192,12 @@
       <c r="N246" t="n">
         <v>0.22</v>
       </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -14768,6 +16256,12 @@
       <c r="N247" t="n">
         <v>0.22</v>
       </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -14826,6 +16320,12 @@
       <c r="N248" t="n">
         <v>0.22</v>
       </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -14884,6 +16384,12 @@
       <c r="N249" t="n">
         <v>0.154</v>
       </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -14942,6 +16448,12 @@
       <c r="N250" t="n">
         <v>0.22</v>
       </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -15000,6 +16512,12 @@
       <c r="N251" t="n">
         <v>0.22</v>
       </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -15058,6 +16576,12 @@
       <c r="N252" t="n">
         <v>0.22</v>
       </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -15116,6 +16640,12 @@
       <c r="N253" t="n">
         <v>0.22</v>
       </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -15174,6 +16704,12 @@
       <c r="N254" t="n">
         <v>0.154</v>
       </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -15232,6 +16768,12 @@
       <c r="N255" t="n">
         <v>0.22</v>
       </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -15290,6 +16832,12 @@
       <c r="N256" t="n">
         <v>0.22</v>
       </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -15348,6 +16896,12 @@
       <c r="N257" t="n">
         <v>0.22</v>
       </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -15406,6 +16960,12 @@
       <c r="N258" t="n">
         <v>0.22</v>
       </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -15464,6 +17024,12 @@
       <c r="N259" t="n">
         <v>0.154</v>
       </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -15522,6 +17088,12 @@
       <c r="N260" t="n">
         <v>0.22</v>
       </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -15580,6 +17152,12 @@
       <c r="N261" t="n">
         <v>0.08799999999999999</v>
       </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -15638,6 +17216,12 @@
       <c r="N262" t="n">
         <v>0.2</v>
       </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -15696,6 +17280,12 @@
       <c r="N263" t="n">
         <v>0.2</v>
       </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -15754,6 +17344,12 @@
       <c r="N264" t="n">
         <v>0.2</v>
       </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -15812,6 +17408,12 @@
       <c r="N265" t="n">
         <v>0.2</v>
       </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -15870,6 +17472,12 @@
       <c r="N266" t="n">
         <v>0.14</v>
       </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -15928,6 +17536,12 @@
       <c r="N267" t="n">
         <v>0.2</v>
       </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -15986,6 +17600,12 @@
       <c r="N268" t="n">
         <v>0.2</v>
       </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -16044,6 +17664,12 @@
       <c r="N269" t="n">
         <v>0.2</v>
       </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -16102,6 +17728,12 @@
       <c r="N270" t="n">
         <v>0.2</v>
       </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -16160,6 +17792,12 @@
       <c r="N271" t="n">
         <v>0.14</v>
       </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -16218,6 +17856,12 @@
       <c r="N272" t="n">
         <v>0.2</v>
       </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -16276,6 +17920,12 @@
       <c r="N273" t="n">
         <v>0.2</v>
       </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -16334,6 +17984,12 @@
       <c r="N274" t="n">
         <v>0.2</v>
       </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -16392,6 +18048,12 @@
       <c r="N275" t="n">
         <v>0.2</v>
       </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -16450,6 +18112,12 @@
       <c r="N276" t="n">
         <v>0.14</v>
       </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -16508,6 +18176,12 @@
       <c r="N277" t="n">
         <v>0.2</v>
       </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -16566,6 +18240,12 @@
       <c r="N278" t="n">
         <v>0.08</v>
       </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -16624,6 +18304,12 @@
       <c r="N279" t="n">
         <v>0.18</v>
       </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -16682,6 +18368,12 @@
       <c r="N280" t="n">
         <v>0.18</v>
       </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -16740,6 +18432,12 @@
       <c r="N281" t="n">
         <v>0.18</v>
       </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -16798,6 +18496,12 @@
       <c r="N282" t="n">
         <v>0.18</v>
       </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -16856,6 +18560,12 @@
       <c r="N283" t="n">
         <v>0.126</v>
       </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -16914,6 +18624,12 @@
       <c r="N284" t="n">
         <v>0.18</v>
       </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -16972,6 +18688,12 @@
       <c r="N285" t="n">
         <v>0.18</v>
       </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -17030,6 +18752,12 @@
       <c r="N286" t="n">
         <v>0.18</v>
       </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -17088,6 +18816,12 @@
       <c r="N287" t="n">
         <v>0.18</v>
       </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -17146,6 +18880,12 @@
       <c r="N288" t="n">
         <v>0.126</v>
       </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -17204,6 +18944,12 @@
       <c r="N289" t="n">
         <v>0.18</v>
       </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -17262,6 +19008,12 @@
       <c r="N290" t="n">
         <v>0.18</v>
       </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -17320,6 +19072,12 @@
       <c r="N291" t="n">
         <v>0.18</v>
       </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -17378,6 +19136,12 @@
       <c r="N292" t="n">
         <v>0.18</v>
       </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -17436,6 +19200,12 @@
       <c r="N293" t="n">
         <v>0.126</v>
       </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -17494,6 +19264,12 @@
       <c r="N294" t="n">
         <v>0.18</v>
       </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -17552,6 +19328,12 @@
       <c r="N295" t="n">
         <v>0.07199999999999999</v>
       </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -17610,6 +19392,12 @@
       <c r="N296" t="n">
         <v>0.16</v>
       </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -17668,6 +19456,12 @@
       <c r="N297" t="n">
         <v>0.16</v>
       </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -17726,6 +19520,12 @@
       <c r="N298" t="n">
         <v>0.16</v>
       </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -17784,6 +19584,12 @@
       <c r="N299" t="n">
         <v>0.16</v>
       </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -17842,6 +19648,12 @@
       <c r="N300" t="n">
         <v>0.112</v>
       </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
+      <c r="P300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -17900,6 +19712,12 @@
       <c r="N301" t="n">
         <v>0.16</v>
       </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -17958,6 +19776,12 @@
       <c r="N302" t="n">
         <v>0.16</v>
       </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -18016,6 +19840,12 @@
       <c r="N303" t="n">
         <v>0.16</v>
       </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -18074,6 +19904,12 @@
       <c r="N304" t="n">
         <v>0.16</v>
       </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -18132,6 +19968,12 @@
       <c r="N305" t="n">
         <v>0.112</v>
       </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -18190,6 +20032,12 @@
       <c r="N306" t="n">
         <v>0.16</v>
       </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -18248,6 +20096,12 @@
       <c r="N307" t="n">
         <v>0.16</v>
       </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -18306,6 +20160,12 @@
       <c r="N308" t="n">
         <v>0.16</v>
       </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -18364,6 +20224,12 @@
       <c r="N309" t="n">
         <v>0.16</v>
       </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -18422,6 +20288,12 @@
       <c r="N310" t="n">
         <v>0.112</v>
       </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
+      <c r="P310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -18480,6 +20352,12 @@
       <c r="N311" t="n">
         <v>0.16</v>
       </c>
+      <c r="O311" t="n">
+        <v>0</v>
+      </c>
+      <c r="P311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -18538,6 +20416,12 @@
       <c r="N312" t="n">
         <v>0.064</v>
       </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -18596,6 +20480,12 @@
       <c r="N313" t="n">
         <v>0.14</v>
       </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -18654,6 +20544,12 @@
       <c r="N314" t="n">
         <v>0.14</v>
       </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -18712,6 +20608,12 @@
       <c r="N315" t="n">
         <v>0.14</v>
       </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -18770,6 +20672,12 @@
       <c r="N316" t="n">
         <v>0.14</v>
       </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -18828,6 +20736,12 @@
       <c r="N317" t="n">
         <v>0.098</v>
       </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -18886,6 +20800,12 @@
       <c r="N318" t="n">
         <v>0.14</v>
       </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -18944,6 +20864,12 @@
       <c r="N319" t="n">
         <v>0.14</v>
       </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -19002,6 +20928,12 @@
       <c r="N320" t="n">
         <v>0.14</v>
       </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -19060,6 +20992,12 @@
       <c r="N321" t="n">
         <v>0.14</v>
       </c>
+      <c r="O321" t="n">
+        <v>0</v>
+      </c>
+      <c r="P321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -19118,6 +21056,12 @@
       <c r="N322" t="n">
         <v>0.098</v>
       </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
+      <c r="P322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -19176,6 +21120,12 @@
       <c r="N323" t="n">
         <v>0.14</v>
       </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -19234,6 +21184,12 @@
       <c r="N324" t="n">
         <v>0.14</v>
       </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -19292,6 +21248,12 @@
       <c r="N325" t="n">
         <v>0.14</v>
       </c>
+      <c r="O325" t="n">
+        <v>0</v>
+      </c>
+      <c r="P325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -19350,6 +21312,12 @@
       <c r="N326" t="n">
         <v>0.14</v>
       </c>
+      <c r="O326" t="n">
+        <v>0</v>
+      </c>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -19408,6 +21376,12 @@
       <c r="N327" t="n">
         <v>0.098</v>
       </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -19466,6 +21440,12 @@
       <c r="N328" t="n">
         <v>0.14</v>
       </c>
+      <c r="O328" t="n">
+        <v>0</v>
+      </c>
+      <c r="P328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -19524,6 +21504,12 @@
       <c r="N329" t="n">
         <v>0.056</v>
       </c>
+      <c r="O329" t="n">
+        <v>0</v>
+      </c>
+      <c r="P329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -19582,6 +21568,12 @@
       <c r="N330" t="n">
         <v>0.12</v>
       </c>
+      <c r="O330" t="n">
+        <v>0</v>
+      </c>
+      <c r="P330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -19640,6 +21632,12 @@
       <c r="N331" t="n">
         <v>0.12</v>
       </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
+      <c r="P331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -19698,6 +21696,12 @@
       <c r="N332" t="n">
         <v>0.12</v>
       </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="P332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -19756,6 +21760,12 @@
       <c r="N333" t="n">
         <v>0.12</v>
       </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="P333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -19814,6 +21824,12 @@
       <c r="N334" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="P334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -19872,6 +21888,12 @@
       <c r="N335" t="n">
         <v>0.12</v>
       </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -19930,6 +21952,12 @@
       <c r="N336" t="n">
         <v>0.12</v>
       </c>
+      <c r="O336" t="n">
+        <v>0</v>
+      </c>
+      <c r="P336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -19988,6 +22016,12 @@
       <c r="N337" t="n">
         <v>0.12</v>
       </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -20046,6 +22080,12 @@
       <c r="N338" t="n">
         <v>0.12</v>
       </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -20104,6 +22144,12 @@
       <c r="N339" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O339" t="n">
+        <v>0</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -20162,6 +22208,12 @@
       <c r="N340" t="n">
         <v>0.12</v>
       </c>
+      <c r="O340" t="n">
+        <v>0</v>
+      </c>
+      <c r="P340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -20220,6 +22272,12 @@
       <c r="N341" t="n">
         <v>0.12</v>
       </c>
+      <c r="O341" t="n">
+        <v>0</v>
+      </c>
+      <c r="P341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -20278,6 +22336,12 @@
       <c r="N342" t="n">
         <v>0.12</v>
       </c>
+      <c r="O342" t="n">
+        <v>0</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -20336,6 +22400,12 @@
       <c r="N343" t="n">
         <v>0.12</v>
       </c>
+      <c r="O343" t="n">
+        <v>0</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -20394,6 +22464,12 @@
       <c r="N344" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O344" t="n">
+        <v>0</v>
+      </c>
+      <c r="P344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -20452,6 +22528,12 @@
       <c r="N345" t="n">
         <v>0.12</v>
       </c>
+      <c r="O345" t="n">
+        <v>0</v>
+      </c>
+      <c r="P345" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -20510,6 +22592,12 @@
       <c r="N346" t="n">
         <v>0.048</v>
       </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
+      <c r="P346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -20568,6 +22656,12 @@
       <c r="N347" t="n">
         <v>0.3</v>
       </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
+      <c r="P347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -20626,6 +22720,12 @@
       <c r="N348" t="n">
         <v>0.3</v>
       </c>
+      <c r="O348" t="n">
+        <v>0</v>
+      </c>
+      <c r="P348" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -20684,6 +22784,12 @@
       <c r="N349" t="n">
         <v>0.3</v>
       </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
+      <c r="P349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -20742,6 +22848,12 @@
       <c r="N350" t="n">
         <v>0.3</v>
       </c>
+      <c r="O350" t="n">
+        <v>0</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -20800,6 +22912,12 @@
       <c r="N351" t="n">
         <v>0.21</v>
       </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
+      <c r="P351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -20858,6 +22976,12 @@
       <c r="N352" t="n">
         <v>0.3</v>
       </c>
+      <c r="O352" t="n">
+        <v>0</v>
+      </c>
+      <c r="P352" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -20916,6 +23040,12 @@
       <c r="N353" t="n">
         <v>0.3</v>
       </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+      <c r="P353" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -20974,6 +23104,12 @@
       <c r="N354" t="n">
         <v>0.3</v>
       </c>
+      <c r="O354" t="n">
+        <v>0</v>
+      </c>
+      <c r="P354" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -21032,6 +23168,12 @@
       <c r="N355" t="n">
         <v>0.3</v>
       </c>
+      <c r="O355" t="n">
+        <v>0</v>
+      </c>
+      <c r="P355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -21090,6 +23232,12 @@
       <c r="N356" t="n">
         <v>0.21</v>
       </c>
+      <c r="O356" t="n">
+        <v>0</v>
+      </c>
+      <c r="P356" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -21148,6 +23296,12 @@
       <c r="N357" t="n">
         <v>0.3</v>
       </c>
+      <c r="O357" t="n">
+        <v>0</v>
+      </c>
+      <c r="P357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -21206,6 +23360,12 @@
       <c r="N358" t="n">
         <v>0.3</v>
       </c>
+      <c r="O358" t="n">
+        <v>0</v>
+      </c>
+      <c r="P358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -21264,6 +23424,12 @@
       <c r="N359" t="n">
         <v>0.3</v>
       </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+      <c r="P359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -21322,6 +23488,12 @@
       <c r="N360" t="n">
         <v>0.3</v>
       </c>
+      <c r="O360" t="n">
+        <v>0</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -21380,6 +23552,12 @@
       <c r="N361" t="n">
         <v>0.21</v>
       </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -21438,6 +23616,12 @@
       <c r="N362" t="n">
         <v>0.12</v>
       </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -21496,6 +23680,12 @@
       <c r="N363" t="n">
         <v>0.28</v>
       </c>
+      <c r="O363" t="n">
+        <v>0</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -21554,6 +23744,12 @@
       <c r="N364" t="n">
         <v>0.28</v>
       </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -21612,6 +23808,12 @@
       <c r="N365" t="n">
         <v>0.28</v>
       </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -21670,6 +23872,12 @@
       <c r="N366" t="n">
         <v>0.28</v>
       </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
+      <c r="P366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -21728,6 +23936,12 @@
       <c r="N367" t="n">
         <v>0.196</v>
       </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -21786,6 +24000,12 @@
       <c r="N368" t="n">
         <v>0.28</v>
       </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -21844,6 +24064,12 @@
       <c r="N369" t="n">
         <v>0.28</v>
       </c>
+      <c r="O369" t="n">
+        <v>0</v>
+      </c>
+      <c r="P369" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -21902,6 +24128,12 @@
       <c r="N370" t="n">
         <v>0.28</v>
       </c>
+      <c r="O370" t="n">
+        <v>0</v>
+      </c>
+      <c r="P370" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -21960,6 +24192,12 @@
       <c r="N371" t="n">
         <v>0.28</v>
       </c>
+      <c r="O371" t="n">
+        <v>0</v>
+      </c>
+      <c r="P371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -22018,6 +24256,12 @@
       <c r="N372" t="n">
         <v>0.196</v>
       </c>
+      <c r="O372" t="n">
+        <v>0</v>
+      </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -22076,6 +24320,12 @@
       <c r="N373" t="n">
         <v>0.28</v>
       </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -22134,6 +24384,12 @@
       <c r="N374" t="n">
         <v>0.28</v>
       </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -22192,6 +24448,12 @@
       <c r="N375" t="n">
         <v>0.28</v>
       </c>
+      <c r="O375" t="n">
+        <v>0</v>
+      </c>
+      <c r="P375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -22250,6 +24512,12 @@
       <c r="N376" t="n">
         <v>0.28</v>
       </c>
+      <c r="O376" t="n">
+        <v>0</v>
+      </c>
+      <c r="P376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -22308,6 +24576,12 @@
       <c r="N377" t="n">
         <v>0.196</v>
       </c>
+      <c r="O377" t="n">
+        <v>0</v>
+      </c>
+      <c r="P377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -22366,6 +24640,12 @@
       <c r="N378" t="n">
         <v>0.112</v>
       </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -22424,6 +24704,12 @@
       <c r="N379" t="n">
         <v>0.26</v>
       </c>
+      <c r="O379" t="n">
+        <v>0</v>
+      </c>
+      <c r="P379" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -22482,6 +24768,12 @@
       <c r="N380" t="n">
         <v>0.26</v>
       </c>
+      <c r="O380" t="n">
+        <v>0</v>
+      </c>
+      <c r="P380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -22540,6 +24832,12 @@
       <c r="N381" t="n">
         <v>0.26</v>
       </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
+      <c r="P381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -22598,6 +24896,12 @@
       <c r="N382" t="n">
         <v>0.26</v>
       </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="P382" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -22656,6 +24960,12 @@
       <c r="N383" t="n">
         <v>0.182</v>
       </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="P383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -22714,6 +25024,12 @@
       <c r="N384" t="n">
         <v>0.26</v>
       </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="P384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -22772,6 +25088,12 @@
       <c r="N385" t="n">
         <v>0.26</v>
       </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -22830,6 +25152,12 @@
       <c r="N386" t="n">
         <v>0.26</v>
       </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -22888,6 +25216,12 @@
       <c r="N387" t="n">
         <v>0.26</v>
       </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -22946,6 +25280,12 @@
       <c r="N388" t="n">
         <v>0.182</v>
       </c>
+      <c r="O388" t="n">
+        <v>0</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -23004,6 +25344,12 @@
       <c r="N389" t="n">
         <v>0.26</v>
       </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -23062,6 +25408,12 @@
       <c r="N390" t="n">
         <v>0.26</v>
       </c>
+      <c r="O390" t="n">
+        <v>0</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -23120,6 +25472,12 @@
       <c r="N391" t="n">
         <v>0.26</v>
       </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -23178,6 +25536,12 @@
       <c r="N392" t="n">
         <v>0.26</v>
       </c>
+      <c r="O392" t="n">
+        <v>0</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -23236,6 +25600,12 @@
       <c r="N393" t="n">
         <v>0.182</v>
       </c>
+      <c r="O393" t="n">
+        <v>0</v>
+      </c>
+      <c r="P393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -23294,6 +25664,12 @@
       <c r="N394" t="n">
         <v>0.104</v>
       </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -23352,6 +25728,12 @@
       <c r="N395" t="n">
         <v>0.24</v>
       </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -23410,6 +25792,12 @@
       <c r="N396" t="n">
         <v>0.24</v>
       </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -23468,6 +25856,12 @@
       <c r="N397" t="n">
         <v>0.24</v>
       </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -23526,6 +25920,12 @@
       <c r="N398" t="n">
         <v>0.24</v>
       </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -23584,6 +25984,12 @@
       <c r="N399" t="n">
         <v>0.168</v>
       </c>
+      <c r="O399" t="n">
+        <v>0</v>
+      </c>
+      <c r="P399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -23642,6 +26048,12 @@
       <c r="N400" t="n">
         <v>0.24</v>
       </c>
+      <c r="O400" t="n">
+        <v>0</v>
+      </c>
+      <c r="P400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -23700,6 +26112,12 @@
       <c r="N401" t="n">
         <v>0.24</v>
       </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+      <c r="P401" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -23758,6 +26176,12 @@
       <c r="N402" t="n">
         <v>0.24</v>
       </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -23816,6 +26240,12 @@
       <c r="N403" t="n">
         <v>0.24</v>
       </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -23874,6 +26304,12 @@
       <c r="N404" t="n">
         <v>0.168</v>
       </c>
+      <c r="O404" t="n">
+        <v>0</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -23932,6 +26368,12 @@
       <c r="N405" t="n">
         <v>0.24</v>
       </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -23990,6 +26432,12 @@
       <c r="N406" t="n">
         <v>0.24</v>
       </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -24048,6 +26496,12 @@
       <c r="N407" t="n">
         <v>0.24</v>
       </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -24106,6 +26560,12 @@
       <c r="N408" t="n">
         <v>0.24</v>
       </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -24164,6 +26624,12 @@
       <c r="N409" t="n">
         <v>0.168</v>
       </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -24222,6 +26688,12 @@
       <c r="N410" t="n">
         <v>0.096</v>
       </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -24280,6 +26752,12 @@
       <c r="N411" t="n">
         <v>0.22</v>
       </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -24338,6 +26816,12 @@
       <c r="N412" t="n">
         <v>0.22</v>
       </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -24396,6 +26880,12 @@
       <c r="N413" t="n">
         <v>0.22</v>
       </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -24454,6 +26944,12 @@
       <c r="N414" t="n">
         <v>0.22</v>
       </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -24512,6 +27008,12 @@
       <c r="N415" t="n">
         <v>0.154</v>
       </c>
+      <c r="O415" t="n">
+        <v>0</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -24570,6 +27072,12 @@
       <c r="N416" t="n">
         <v>0.22</v>
       </c>
+      <c r="O416" t="n">
+        <v>0</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -24628,6 +27136,12 @@
       <c r="N417" t="n">
         <v>0.22</v>
       </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -24686,6 +27200,12 @@
       <c r="N418" t="n">
         <v>0.22</v>
       </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -24744,6 +27264,12 @@
       <c r="N419" t="n">
         <v>0.22</v>
       </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -24802,6 +27328,12 @@
       <c r="N420" t="n">
         <v>0.154</v>
       </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+      <c r="P420" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -24860,6 +27392,12 @@
       <c r="N421" t="n">
         <v>0.22</v>
       </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -24918,6 +27456,12 @@
       <c r="N422" t="n">
         <v>0.22</v>
       </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+      <c r="P422" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -24976,6 +27520,12 @@
       <c r="N423" t="n">
         <v>0.22</v>
       </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -25034,6 +27584,12 @@
       <c r="N424" t="n">
         <v>0.22</v>
       </c>
+      <c r="O424" t="n">
+        <v>0</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -25092,6 +27648,12 @@
       <c r="N425" t="n">
         <v>0.154</v>
       </c>
+      <c r="O425" t="n">
+        <v>0</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -25150,6 +27712,12 @@
       <c r="N426" t="n">
         <v>0.08799999999999999</v>
       </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -25208,6 +27776,12 @@
       <c r="N427" t="n">
         <v>0.2</v>
       </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -25266,6 +27840,12 @@
       <c r="N428" t="n">
         <v>0.2</v>
       </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -25324,6 +27904,12 @@
       <c r="N429" t="n">
         <v>0.2</v>
       </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -25382,6 +27968,12 @@
       <c r="N430" t="n">
         <v>0.2</v>
       </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -25440,6 +28032,12 @@
       <c r="N431" t="n">
         <v>0.14</v>
       </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -25498,6 +28096,12 @@
       <c r="N432" t="n">
         <v>0.2</v>
       </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -25556,6 +28160,12 @@
       <c r="N433" t="n">
         <v>0.2</v>
       </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -25614,6 +28224,12 @@
       <c r="N434" t="n">
         <v>0.2</v>
       </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -25672,6 +28288,12 @@
       <c r="N435" t="n">
         <v>0.2</v>
       </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -25730,6 +28352,12 @@
       <c r="N436" t="n">
         <v>0.14</v>
       </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="P436" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -25788,6 +28416,12 @@
       <c r="N437" t="n">
         <v>0.2</v>
       </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -25846,6 +28480,12 @@
       <c r="N438" t="n">
         <v>0.2</v>
       </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -25904,6 +28544,12 @@
       <c r="N439" t="n">
         <v>0.2</v>
       </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -25962,6 +28608,12 @@
       <c r="N440" t="n">
         <v>0.2</v>
       </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -26020,6 +28672,12 @@
       <c r="N441" t="n">
         <v>0.14</v>
       </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -26078,6 +28736,12 @@
       <c r="N442" t="n">
         <v>0.08</v>
       </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -26136,6 +28800,12 @@
       <c r="N443" t="n">
         <v>0.18</v>
       </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -26194,6 +28864,12 @@
       <c r="N444" t="n">
         <v>0.18</v>
       </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -26252,6 +28928,12 @@
       <c r="N445" t="n">
         <v>0.18</v>
       </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -26310,6 +28992,12 @@
       <c r="N446" t="n">
         <v>0.18</v>
       </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -26368,6 +29056,12 @@
       <c r="N447" t="n">
         <v>0.126</v>
       </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -26426,6 +29120,12 @@
       <c r="N448" t="n">
         <v>0.18</v>
       </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="P448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -26484,6 +29184,12 @@
       <c r="N449" t="n">
         <v>0.18</v>
       </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -26542,6 +29248,12 @@
       <c r="N450" t="n">
         <v>0.18</v>
       </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -26600,6 +29312,12 @@
       <c r="N451" t="n">
         <v>0.18</v>
       </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -26658,6 +29376,12 @@
       <c r="N452" t="n">
         <v>0.126</v>
       </c>
+      <c r="O452" t="n">
+        <v>0</v>
+      </c>
+      <c r="P452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -26716,6 +29440,12 @@
       <c r="N453" t="n">
         <v>0.18</v>
       </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+      <c r="P453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -26774,6 +29504,12 @@
       <c r="N454" t="n">
         <v>0.18</v>
       </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
+      <c r="P454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -26832,6 +29568,12 @@
       <c r="N455" t="n">
         <v>0.18</v>
       </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -26890,6 +29632,12 @@
       <c r="N456" t="n">
         <v>0.18</v>
       </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -26948,6 +29696,12 @@
       <c r="N457" t="n">
         <v>0.126</v>
       </c>
+      <c r="O457" t="n">
+        <v>0</v>
+      </c>
+      <c r="P457" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -27006,6 +29760,12 @@
       <c r="N458" t="n">
         <v>0.07199999999999999</v>
       </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+      <c r="P458" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -27064,6 +29824,12 @@
       <c r="N459" t="n">
         <v>0.16</v>
       </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -27122,6 +29888,12 @@
       <c r="N460" t="n">
         <v>0.16</v>
       </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+      <c r="P460" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -27180,6 +29952,12 @@
       <c r="N461" t="n">
         <v>0.16</v>
       </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="P461" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -27238,6 +30016,12 @@
       <c r="N462" t="n">
         <v>0.16</v>
       </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="P462" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -27296,6 +30080,12 @@
       <c r="N463" t="n">
         <v>0.112</v>
       </c>
+      <c r="O463" t="n">
+        <v>0</v>
+      </c>
+      <c r="P463" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -27354,6 +30144,12 @@
       <c r="N464" t="n">
         <v>0.16</v>
       </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -27412,6 +30208,12 @@
       <c r="N465" t="n">
         <v>0.16</v>
       </c>
+      <c r="O465" t="n">
+        <v>0</v>
+      </c>
+      <c r="P465" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -27470,6 +30272,12 @@
       <c r="N466" t="n">
         <v>0.16</v>
       </c>
+      <c r="O466" t="n">
+        <v>0</v>
+      </c>
+      <c r="P466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -27528,6 +30336,12 @@
       <c r="N467" t="n">
         <v>0.16</v>
       </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
+      <c r="P467" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -27586,6 +30400,12 @@
       <c r="N468" t="n">
         <v>0.112</v>
       </c>
+      <c r="O468" t="n">
+        <v>0</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -27644,6 +30464,12 @@
       <c r="N469" t="n">
         <v>0.16</v>
       </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -27702,6 +30528,12 @@
       <c r="N470" t="n">
         <v>0.16</v>
       </c>
+      <c r="O470" t="n">
+        <v>0</v>
+      </c>
+      <c r="P470" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -27760,6 +30592,12 @@
       <c r="N471" t="n">
         <v>0.16</v>
       </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -27818,6 +30656,12 @@
       <c r="N472" t="n">
         <v>0.16</v>
       </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
+      <c r="P472" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -27876,6 +30720,12 @@
       <c r="N473" t="n">
         <v>0.112</v>
       </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -27934,6 +30784,12 @@
       <c r="N474" t="n">
         <v>0.064</v>
       </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -27992,6 +30848,12 @@
       <c r="N475" t="n">
         <v>0.14</v>
       </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="P475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -28050,6 +30912,12 @@
       <c r="N476" t="n">
         <v>0.14</v>
       </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -28108,6 +30976,12 @@
       <c r="N477" t="n">
         <v>0.14</v>
       </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
+      <c r="P477" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -28166,6 +31040,12 @@
       <c r="N478" t="n">
         <v>0.14</v>
       </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
+      <c r="P478" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -28224,6 +31104,12 @@
       <c r="N479" t="n">
         <v>0.098</v>
       </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
+      <c r="P479" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -28282,6 +31168,12 @@
       <c r="N480" t="n">
         <v>0.14</v>
       </c>
+      <c r="O480" t="n">
+        <v>0</v>
+      </c>
+      <c r="P480" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -28340,6 +31232,12 @@
       <c r="N481" t="n">
         <v>0.14</v>
       </c>
+      <c r="O481" t="n">
+        <v>0</v>
+      </c>
+      <c r="P481" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -28398,6 +31296,12 @@
       <c r="N482" t="n">
         <v>0.14</v>
       </c>
+      <c r="O482" t="n">
+        <v>0</v>
+      </c>
+      <c r="P482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -28456,6 +31360,12 @@
       <c r="N483" t="n">
         <v>0.14</v>
       </c>
+      <c r="O483" t="n">
+        <v>0</v>
+      </c>
+      <c r="P483" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -28514,6 +31424,12 @@
       <c r="N484" t="n">
         <v>0.098</v>
       </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -28572,6 +31488,12 @@
       <c r="N485" t="n">
         <v>0.14</v>
       </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -28630,6 +31552,12 @@
       <c r="N486" t="n">
         <v>0.14</v>
       </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -28688,6 +31616,12 @@
       <c r="N487" t="n">
         <v>0.14</v>
       </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -28746,6 +31680,12 @@
       <c r="N488" t="n">
         <v>0.14</v>
       </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -28804,6 +31744,12 @@
       <c r="N489" t="n">
         <v>0.098</v>
       </c>
+      <c r="O489" t="n">
+        <v>0</v>
+      </c>
+      <c r="P489" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -28862,6 +31808,12 @@
       <c r="N490" t="n">
         <v>0.056</v>
       </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
+      <c r="P490" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -28920,6 +31872,12 @@
       <c r="N491" t="n">
         <v>0.12</v>
       </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -28978,6 +31936,12 @@
       <c r="N492" t="n">
         <v>0.12</v>
       </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -29036,6 +32000,12 @@
       <c r="N493" t="n">
         <v>0.12</v>
       </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -29094,6 +32064,12 @@
       <c r="N494" t="n">
         <v>0.12</v>
       </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
+      <c r="P494" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -29152,6 +32128,12 @@
       <c r="N495" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
+      <c r="P495" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -29210,6 +32192,12 @@
       <c r="N496" t="n">
         <v>0.12</v>
       </c>
+      <c r="O496" t="n">
+        <v>0</v>
+      </c>
+      <c r="P496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -29268,6 +32256,12 @@
       <c r="N497" t="n">
         <v>0.12</v>
       </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -29326,6 +32320,12 @@
       <c r="N498" t="n">
         <v>0.12</v>
       </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
+      <c r="P498" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -29384,6 +32384,12 @@
       <c r="N499" t="n">
         <v>0.12</v>
       </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
+      <c r="P499" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -29442,6 +32448,12 @@
       <c r="N500" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -29500,6 +32512,12 @@
       <c r="N501" t="n">
         <v>0.12</v>
       </c>
+      <c r="O501" t="n">
+        <v>0</v>
+      </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -29558,6 +32576,12 @@
       <c r="N502" t="n">
         <v>0.12</v>
       </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -29616,6 +32640,12 @@
       <c r="N503" t="n">
         <v>0.12</v>
       </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -29674,6 +32704,12 @@
       <c r="N504" t="n">
         <v>0.12</v>
       </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -29732,6 +32768,12 @@
       <c r="N505" t="n">
         <v>0.08400000000000001</v>
       </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -29789,6 +32831,12 @@
       </c>
       <c r="N506" t="n">
         <v>0.048</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
